--- a/enrollment/fileTemplates/student&sectionTemplates/student(XLSX).xlsx
+++ b/enrollment/fileTemplates/student&sectionTemplates/student(XLSX).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d725c04a17b73256/Documents/Programming/VSCode/CAPSTONE-preEnrollment/preEnrollmentV6.2/enrollment/fileTemplates/student^0sectionTemplates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d725c04a17b73256/Documents/Pre Enrollment File Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{4A12666A-672B-4379-9E11-03BF66B8A6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F85AC3-BF91-48DD-83B3-49AD521C19C9}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{4A12666A-672B-4379-9E11-03BF66B8A6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A3802A4-19E1-4F20-8288-D2CC81BFCBB6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{32C72668-5EA3-4148-AB22-E6FC3855149B}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>A</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Enrolled</t>
   </si>
@@ -43,19 +40,16 @@
     <t>YEAR</t>
   </si>
   <si>
-    <t>SECTION</t>
-  </si>
-  <si>
     <t>SEMESTER</t>
   </si>
   <si>
     <t>STATUS</t>
   </si>
   <si>
-    <t>Jerry</t>
+    <t>Hera Eryza</t>
   </si>
   <si>
-    <t>Corazon</t>
+    <t>Dagohoy</t>
   </si>
 </sst>
 </file>
@@ -925,58 +919,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F329A3CF-F485-47C1-B091-9F3169CDB046}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
     <col min="2" max="3" width="12.77734375" customWidth="1"/>
-    <col min="4" max="7" width="9.77734375" customWidth="1"/>
+    <col min="4" max="6" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>202610080</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>202310017</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
       <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
